--- a/assets/MAU_BURN_TEST_REPORT.xlsx
+++ b/assets/MAU_BURN_TEST_REPORT.xlsx
@@ -304,7 +304,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -361,9 +361,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="30"/>
-      <name val="Segoe Script"/>
+      <sz val="72"/>
+      <name val="TH Manchester Signature Alt"/>
       <charset val="134"/>
     </font>
     <font>
@@ -429,6 +428,12 @@
     <font>
       <sz val="14"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="60"/>
+      <name val="TH Manchester Signature"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1271,138 +1276,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="32" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="37" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="35" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="37" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1511,12 +1516,18 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="58" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1718,7 +1729,10 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2044,20 +2058,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>219710</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>69215</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>425450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>589280</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114935</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="hieu"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2070,16 +2084,50 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3143885" y="30262830"/>
-          <a:ext cx="1513840" cy="814705"/>
+          <a:off x="16249650" y="4376420"/>
+          <a:ext cx="1265555" cy="680085"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>407670</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>260985</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>815340</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>2540</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5" descr="hieu"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3331845" y="30159325"/>
+          <a:ext cx="1407795" cy="760730"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2656,7 +2704,7 @@
   <sheetPr>
     <tabColor rgb="FFA9A3BF"/>
   </sheetPr>
-  <dimension ref="A1:T81"/>
+  <dimension ref="A1:T83"/>
   <sheetFormatPr defaultColWidth="13.8571428571429" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.1428571428571" style="3" customWidth="1"/>
@@ -2885,27 +2933,27 @@
       <c r="L9" s="29"/>
       <c r="M9" s="29"/>
       <c r="N9" s="37"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="33"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="39"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:20">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40" t="s">
+      <c r="B10" s="41"/>
+      <c r="C10" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="42"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="44"/>
       <c r="J10" s="28" t="s">
         <v>16</v>
       </c>
@@ -2921,15 +2969,15 @@
       <c r="T10" s="33"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="39" customHeight="1" spans="1:20">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="47"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="49"/>
       <c r="J11" s="28" t="s">
         <v>17</v>
       </c>
@@ -2945,1614 +2993,1627 @@
       <c r="T11" s="33"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="21.95" customHeight="1" spans="1:20">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50" t="s">
+      <c r="B12" s="51"/>
+      <c r="C12" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="51" t="s">
+      <c r="G12" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="50" t="s">
+      <c r="H12" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="50" t="s">
+      <c r="I12" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="50" t="s">
+      <c r="J12" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="50" t="s">
+      <c r="K12" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="L12" s="50" t="s">
+      <c r="L12" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="M12" s="50" t="s">
+      <c r="M12" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="N12" s="50" t="s">
+      <c r="N12" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="O12" s="50" t="s">
+      <c r="O12" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="P12" s="50" t="s">
+      <c r="P12" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="Q12" s="50" t="s">
+      <c r="Q12" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="50" t="s">
+      <c r="R12" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="S12" s="50" t="s">
+      <c r="S12" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="T12" s="52" t="s">
+      <c r="T12" s="54" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="18.95" customHeight="1" spans="1:20">
-      <c r="A13" s="48"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="52"/>
+      <c r="A13" s="50"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="52"/>
+      <c r="O13" s="52"/>
+      <c r="P13" s="52"/>
+      <c r="Q13" s="52"/>
+      <c r="R13" s="52"/>
+      <c r="S13" s="52"/>
+      <c r="T13" s="54"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="18.95" customHeight="1" spans="1:20">
-      <c r="A14" s="48"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="50"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="50"/>
-      <c r="P14" s="50"/>
-      <c r="Q14" s="50"/>
-      <c r="R14" s="50"/>
-      <c r="S14" s="50"/>
-      <c r="T14" s="52"/>
+      <c r="A14" s="50"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="52"/>
+      <c r="O14" s="52"/>
+      <c r="P14" s="52"/>
+      <c r="Q14" s="52"/>
+      <c r="R14" s="52"/>
+      <c r="S14" s="52"/>
+      <c r="T14" s="54"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="18.95" customHeight="1" spans="1:20">
-      <c r="A15" s="48"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="50"/>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="50"/>
-      <c r="R15" s="50"/>
-      <c r="S15" s="50"/>
-      <c r="T15" s="52"/>
+      <c r="A15" s="50"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="52"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="52"/>
+      <c r="N15" s="52"/>
+      <c r="O15" s="52"/>
+      <c r="P15" s="52"/>
+      <c r="Q15" s="52"/>
+      <c r="R15" s="52"/>
+      <c r="S15" s="52"/>
+      <c r="T15" s="54"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="18.95" customHeight="1" spans="1:20">
-      <c r="A16" s="48"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="53"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="50"/>
-      <c r="L16" s="50"/>
-      <c r="M16" s="50"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="50"/>
-      <c r="P16" s="50"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="50"/>
-      <c r="S16" s="50"/>
-      <c r="T16" s="52"/>
+      <c r="A16" s="50"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52"/>
+      <c r="P16" s="52"/>
+      <c r="Q16" s="52"/>
+      <c r="R16" s="52"/>
+      <c r="S16" s="52"/>
+      <c r="T16" s="54"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="18.95" customHeight="1" spans="1:20">
-      <c r="A17" s="54"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="50"/>
-      <c r="L17" s="50"/>
-      <c r="M17" s="50"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="50"/>
-      <c r="P17" s="50"/>
-      <c r="Q17" s="50"/>
-      <c r="R17" s="50"/>
-      <c r="S17" s="50"/>
-      <c r="T17" s="52"/>
+      <c r="A17" s="56"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="52"/>
+      <c r="P17" s="52"/>
+      <c r="Q17" s="52"/>
+      <c r="R17" s="52"/>
+      <c r="S17" s="52"/>
+      <c r="T17" s="54"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A18" s="57"/>
-      <c r="B18" s="58">
+      <c r="A18" s="59"/>
+      <c r="B18" s="60">
         <v>1</v>
       </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="59"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="59"/>
-      <c r="L18" s="59"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="59"/>
-      <c r="O18" s="59"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="59"/>
-      <c r="R18" s="59"/>
-      <c r="S18" s="59"/>
-      <c r="T18" s="60"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="61"/>
+      <c r="O18" s="61"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="61"/>
+      <c r="R18" s="61"/>
+      <c r="S18" s="61"/>
+      <c r="T18" s="62"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A19" s="61"/>
-      <c r="B19" s="58">
+      <c r="A19" s="63"/>
+      <c r="B19" s="60">
         <v>2</v>
       </c>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="59"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="59"/>
-      <c r="O19" s="59"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="59"/>
-      <c r="R19" s="59"/>
-      <c r="S19" s="59"/>
-      <c r="T19" s="60"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="61"/>
+      <c r="O19" s="61"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="61"/>
+      <c r="R19" s="61"/>
+      <c r="S19" s="61"/>
+      <c r="T19" s="62"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A20" s="61"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="59"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="59"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="59"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="59"/>
-      <c r="R20" s="59"/>
-      <c r="S20" s="59"/>
-      <c r="T20" s="60"/>
+      <c r="A20" s="63"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="61"/>
+      <c r="S20" s="61"/>
+      <c r="T20" s="62"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A21" s="61"/>
-      <c r="B21" s="58">
+      <c r="A21" s="63"/>
+      <c r="B21" s="60">
         <v>4</v>
       </c>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="59"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="59"/>
-      <c r="R21" s="59"/>
-      <c r="S21" s="59"/>
-      <c r="T21" s="60"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="61"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="61"/>
+      <c r="O21" s="61"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="61"/>
+      <c r="R21" s="61"/>
+      <c r="S21" s="61"/>
+      <c r="T21" s="62"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A22" s="61"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="59"/>
-      <c r="O22" s="59"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="59"/>
-      <c r="R22" s="59"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="60"/>
+      <c r="A22" s="63"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="61"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="61"/>
+      <c r="R22" s="61"/>
+      <c r="S22" s="61"/>
+      <c r="T22" s="62"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A23" s="61"/>
-      <c r="B23" s="58">
+      <c r="A23" s="63"/>
+      <c r="B23" s="60">
         <v>6</v>
       </c>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="59"/>
-      <c r="O23" s="59"/>
-      <c r="P23" s="59"/>
-      <c r="Q23" s="59"/>
-      <c r="R23" s="59"/>
-      <c r="S23" s="59"/>
-      <c r="T23" s="60"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="61"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="61"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="61"/>
+      <c r="T23" s="62"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A24" s="61"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="59"/>
-      <c r="K24" s="59"/>
-      <c r="L24" s="59"/>
-      <c r="M24" s="59"/>
-      <c r="N24" s="59"/>
-      <c r="O24" s="59"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="59"/>
-      <c r="R24" s="59"/>
-      <c r="S24" s="59"/>
-      <c r="T24" s="60"/>
+      <c r="A24" s="63"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="61"/>
+      <c r="O24" s="61"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="61"/>
+      <c r="R24" s="61"/>
+      <c r="S24" s="61"/>
+      <c r="T24" s="62"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A25" s="61"/>
-      <c r="B25" s="58">
+      <c r="A25" s="63"/>
+      <c r="B25" s="60">
         <v>8</v>
       </c>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="59"/>
-      <c r="O25" s="59"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="59"/>
-      <c r="R25" s="59"/>
-      <c r="S25" s="59"/>
-      <c r="T25" s="60"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="61"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="61"/>
+      <c r="O25" s="61"/>
+      <c r="P25" s="61"/>
+      <c r="Q25" s="61"/>
+      <c r="R25" s="61"/>
+      <c r="S25" s="61"/>
+      <c r="T25" s="62"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A26" s="61"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="59"/>
-      <c r="O26" s="59"/>
-      <c r="P26" s="59"/>
-      <c r="Q26" s="59"/>
-      <c r="R26" s="59"/>
-      <c r="S26" s="59"/>
-      <c r="T26" s="60"/>
+      <c r="A26" s="63"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="61"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="61"/>
+      <c r="S26" s="61"/>
+      <c r="T26" s="62"/>
     </row>
     <row r="27" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A27" s="61"/>
-      <c r="B27" s="58">
+      <c r="A27" s="63"/>
+      <c r="B27" s="60">
         <v>10</v>
       </c>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="59"/>
-      <c r="M27" s="59"/>
-      <c r="N27" s="59"/>
-      <c r="O27" s="59"/>
-      <c r="P27" s="59"/>
-      <c r="Q27" s="59"/>
-      <c r="R27" s="59"/>
-      <c r="S27" s="59"/>
-      <c r="T27" s="60"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="61"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="61"/>
+      <c r="O27" s="61"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="61"/>
+      <c r="R27" s="61"/>
+      <c r="S27" s="61"/>
+      <c r="T27" s="62"/>
     </row>
     <row r="28" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A28" s="61"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="59"/>
-      <c r="D28" s="59"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="59"/>
-      <c r="M28" s="59"/>
-      <c r="N28" s="59"/>
-      <c r="O28" s="59"/>
-      <c r="P28" s="59"/>
-      <c r="Q28" s="59"/>
-      <c r="R28" s="59"/>
-      <c r="S28" s="59"/>
-      <c r="T28" s="60"/>
+      <c r="A28" s="63"/>
+      <c r="B28" s="60"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="61"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="61"/>
+      <c r="O28" s="61"/>
+      <c r="P28" s="61"/>
+      <c r="Q28" s="61"/>
+      <c r="R28" s="61"/>
+      <c r="S28" s="61"/>
+      <c r="T28" s="62"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A29" s="61"/>
-      <c r="B29" s="58">
+      <c r="A29" s="63"/>
+      <c r="B29" s="60">
         <v>12</v>
       </c>
-      <c r="C29" s="59"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="59"/>
-      <c r="J29" s="59"/>
-      <c r="K29" s="59"/>
-      <c r="L29" s="59"/>
-      <c r="M29" s="59"/>
-      <c r="N29" s="59"/>
-      <c r="O29" s="59"/>
-      <c r="P29" s="59"/>
-      <c r="Q29" s="59"/>
-      <c r="R29" s="59"/>
-      <c r="S29" s="59"/>
-      <c r="T29" s="60"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="61"/>
+      <c r="K29" s="61"/>
+      <c r="L29" s="61"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="61"/>
+      <c r="O29" s="61"/>
+      <c r="P29" s="61"/>
+      <c r="Q29" s="61"/>
+      <c r="R29" s="61"/>
+      <c r="S29" s="61"/>
+      <c r="T29" s="62"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A30" s="61"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="59"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="59"/>
-      <c r="J30" s="59"/>
-      <c r="K30" s="59"/>
-      <c r="L30" s="59"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="59"/>
-      <c r="O30" s="59"/>
-      <c r="P30" s="59"/>
-      <c r="Q30" s="59"/>
-      <c r="R30" s="59"/>
-      <c r="S30" s="59"/>
-      <c r="T30" s="60"/>
+      <c r="A30" s="63"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="61"/>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="61"/>
+      <c r="R30" s="61"/>
+      <c r="S30" s="61"/>
+      <c r="T30" s="62"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A31" s="61"/>
-      <c r="B31" s="58">
+      <c r="A31" s="63"/>
+      <c r="B31" s="60">
         <v>14</v>
       </c>
-      <c r="C31" s="59"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="59"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="59"/>
-      <c r="M31" s="59"/>
-      <c r="N31" s="59"/>
-      <c r="O31" s="59"/>
-      <c r="P31" s="59"/>
-      <c r="Q31" s="59"/>
-      <c r="R31" s="59"/>
-      <c r="S31" s="59"/>
-      <c r="T31" s="60"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="61"/>
+      <c r="O31" s="61"/>
+      <c r="P31" s="61"/>
+      <c r="Q31" s="61"/>
+      <c r="R31" s="61"/>
+      <c r="S31" s="61"/>
+      <c r="T31" s="62"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A32" s="61"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="59"/>
-      <c r="J32" s="59"/>
-      <c r="K32" s="59"/>
-      <c r="L32" s="59"/>
-      <c r="M32" s="59"/>
-      <c r="N32" s="59"/>
-      <c r="O32" s="59"/>
-      <c r="P32" s="59"/>
-      <c r="Q32" s="59"/>
-      <c r="R32" s="59"/>
-      <c r="S32" s="59"/>
-      <c r="T32" s="60"/>
+      <c r="A32" s="63"/>
+      <c r="B32" s="60"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="61"/>
+      <c r="N32" s="61"/>
+      <c r="O32" s="61"/>
+      <c r="P32" s="61"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="61"/>
+      <c r="S32" s="61"/>
+      <c r="T32" s="62"/>
     </row>
     <row r="33" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A33" s="61"/>
-      <c r="B33" s="58">
+      <c r="A33" s="63"/>
+      <c r="B33" s="60">
         <v>16</v>
       </c>
-      <c r="C33" s="59"/>
-      <c r="D33" s="59"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="59"/>
-      <c r="H33" s="59"/>
-      <c r="I33" s="59"/>
-      <c r="J33" s="59"/>
-      <c r="K33" s="59"/>
-      <c r="L33" s="59"/>
-      <c r="M33" s="59"/>
-      <c r="N33" s="59"/>
-      <c r="O33" s="59"/>
-      <c r="P33" s="59"/>
-      <c r="Q33" s="59"/>
-      <c r="R33" s="59"/>
-      <c r="S33" s="59"/>
-      <c r="T33" s="60"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="61"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="61"/>
+      <c r="L33" s="61"/>
+      <c r="M33" s="61"/>
+      <c r="N33" s="61"/>
+      <c r="O33" s="61"/>
+      <c r="P33" s="61"/>
+      <c r="Q33" s="61"/>
+      <c r="R33" s="61"/>
+      <c r="S33" s="61"/>
+      <c r="T33" s="62"/>
     </row>
     <row r="34" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A34" s="61"/>
-      <c r="B34" s="58"/>
-      <c r="C34" s="59"/>
-      <c r="D34" s="59"/>
-      <c r="E34" s="59"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="59"/>
-      <c r="I34" s="59"/>
-      <c r="J34" s="59"/>
-      <c r="K34" s="59"/>
-      <c r="L34" s="59"/>
-      <c r="M34" s="59"/>
-      <c r="N34" s="59"/>
-      <c r="O34" s="59"/>
-      <c r="P34" s="59"/>
-      <c r="Q34" s="59"/>
-      <c r="R34" s="59"/>
-      <c r="S34" s="59"/>
-      <c r="T34" s="60"/>
+      <c r="A34" s="63"/>
+      <c r="B34" s="60"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="61"/>
+      <c r="N34" s="61"/>
+      <c r="O34" s="61"/>
+      <c r="P34" s="61"/>
+      <c r="Q34" s="61"/>
+      <c r="R34" s="61"/>
+      <c r="S34" s="61"/>
+      <c r="T34" s="62"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A35" s="61"/>
-      <c r="B35" s="58">
+      <c r="A35" s="63"/>
+      <c r="B35" s="60">
         <v>18</v>
       </c>
-      <c r="C35" s="59"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
-      <c r="I35" s="59"/>
-      <c r="J35" s="59"/>
-      <c r="K35" s="59"/>
-      <c r="L35" s="59"/>
-      <c r="M35" s="59"/>
-      <c r="N35" s="59"/>
-      <c r="O35" s="59"/>
-      <c r="P35" s="59"/>
-      <c r="Q35" s="59"/>
-      <c r="R35" s="59"/>
-      <c r="S35" s="59"/>
-      <c r="T35" s="60"/>
+      <c r="C35" s="61"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="61"/>
+      <c r="L35" s="61"/>
+      <c r="M35" s="61"/>
+      <c r="N35" s="61"/>
+      <c r="O35" s="61"/>
+      <c r="P35" s="61"/>
+      <c r="Q35" s="61"/>
+      <c r="R35" s="61"/>
+      <c r="S35" s="61"/>
+      <c r="T35" s="62"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A36" s="61"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
-      <c r="J36" s="59"/>
-      <c r="K36" s="59"/>
-      <c r="L36" s="59"/>
-      <c r="M36" s="59"/>
-      <c r="N36" s="59"/>
-      <c r="O36" s="59"/>
-      <c r="P36" s="59"/>
-      <c r="Q36" s="59"/>
-      <c r="R36" s="59"/>
-      <c r="S36" s="59"/>
-      <c r="T36" s="60"/>
+      <c r="A36" s="63"/>
+      <c r="B36" s="60"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="61"/>
+      <c r="M36" s="61"/>
+      <c r="N36" s="61"/>
+      <c r="O36" s="61"/>
+      <c r="P36" s="61"/>
+      <c r="Q36" s="61"/>
+      <c r="R36" s="61"/>
+      <c r="S36" s="61"/>
+      <c r="T36" s="62"/>
     </row>
     <row r="37" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A37" s="61"/>
-      <c r="B37" s="58">
+      <c r="A37" s="63"/>
+      <c r="B37" s="60">
         <v>20</v>
       </c>
-      <c r="C37" s="59"/>
-      <c r="D37" s="59"/>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="59"/>
-      <c r="K37" s="59"/>
-      <c r="L37" s="59"/>
-      <c r="M37" s="59"/>
-      <c r="N37" s="59"/>
-      <c r="O37" s="59"/>
-      <c r="P37" s="59"/>
-      <c r="Q37" s="59"/>
-      <c r="R37" s="59"/>
-      <c r="S37" s="59"/>
-      <c r="T37" s="60"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="61"/>
+      <c r="N37" s="61"/>
+      <c r="O37" s="61"/>
+      <c r="P37" s="61"/>
+      <c r="Q37" s="61"/>
+      <c r="R37" s="61"/>
+      <c r="S37" s="61"/>
+      <c r="T37" s="62"/>
     </row>
     <row r="38" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A38" s="61"/>
-      <c r="B38" s="58"/>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="59"/>
-      <c r="J38" s="59"/>
-      <c r="K38" s="59"/>
-      <c r="L38" s="59"/>
-      <c r="M38" s="59"/>
-      <c r="N38" s="59"/>
-      <c r="O38" s="59"/>
-      <c r="P38" s="59"/>
-      <c r="Q38" s="59"/>
-      <c r="R38" s="59"/>
-      <c r="S38" s="59"/>
-      <c r="T38" s="60"/>
+      <c r="A38" s="63"/>
+      <c r="B38" s="60"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="61"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="61"/>
+      <c r="M38" s="61"/>
+      <c r="N38" s="61"/>
+      <c r="O38" s="61"/>
+      <c r="P38" s="61"/>
+      <c r="Q38" s="61"/>
+      <c r="R38" s="61"/>
+      <c r="S38" s="61"/>
+      <c r="T38" s="62"/>
     </row>
     <row r="39" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A39" s="61"/>
-      <c r="B39" s="58">
+      <c r="A39" s="63"/>
+      <c r="B39" s="60">
         <v>22</v>
       </c>
-      <c r="C39" s="59"/>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
-      <c r="H39" s="59"/>
-      <c r="I39" s="59"/>
-      <c r="J39" s="59"/>
-      <c r="K39" s="59"/>
-      <c r="L39" s="59"/>
-      <c r="M39" s="59"/>
-      <c r="N39" s="59"/>
-      <c r="O39" s="59"/>
-      <c r="P39" s="59"/>
-      <c r="Q39" s="59"/>
-      <c r="R39" s="59"/>
-      <c r="S39" s="59"/>
-      <c r="T39" s="60"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="61"/>
+      <c r="K39" s="61"/>
+      <c r="L39" s="61"/>
+      <c r="M39" s="61"/>
+      <c r="N39" s="61"/>
+      <c r="O39" s="61"/>
+      <c r="P39" s="61"/>
+      <c r="Q39" s="61"/>
+      <c r="R39" s="61"/>
+      <c r="S39" s="61"/>
+      <c r="T39" s="62"/>
     </row>
     <row r="40" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A40" s="61"/>
-      <c r="B40" s="58"/>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
-      <c r="I40" s="59"/>
-      <c r="J40" s="59"/>
-      <c r="K40" s="59"/>
-      <c r="L40" s="59"/>
-      <c r="M40" s="59"/>
-      <c r="N40" s="59"/>
-      <c r="O40" s="59"/>
-      <c r="P40" s="59"/>
-      <c r="Q40" s="59"/>
-      <c r="R40" s="59"/>
-      <c r="S40" s="59"/>
-      <c r="T40" s="60"/>
+      <c r="A40" s="63"/>
+      <c r="B40" s="60"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="61"/>
+      <c r="M40" s="61"/>
+      <c r="N40" s="61"/>
+      <c r="O40" s="61"/>
+      <c r="P40" s="61"/>
+      <c r="Q40" s="61"/>
+      <c r="R40" s="61"/>
+      <c r="S40" s="61"/>
+      <c r="T40" s="62"/>
     </row>
     <row r="41" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A41" s="61"/>
-      <c r="B41" s="58">
+      <c r="A41" s="63"/>
+      <c r="B41" s="60">
         <v>24</v>
       </c>
-      <c r="C41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="59"/>
-      <c r="F41" s="59"/>
-      <c r="G41" s="59"/>
-      <c r="H41" s="59"/>
-      <c r="I41" s="59"/>
-      <c r="J41" s="59"/>
-      <c r="K41" s="59"/>
-      <c r="L41" s="59"/>
-      <c r="M41" s="59"/>
-      <c r="N41" s="59"/>
-      <c r="O41" s="59"/>
-      <c r="P41" s="59"/>
-      <c r="Q41" s="59"/>
-      <c r="R41" s="59"/>
-      <c r="S41" s="59"/>
-      <c r="T41" s="60"/>
+      <c r="C41" s="61"/>
+      <c r="D41" s="61"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="61"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="61"/>
+      <c r="L41" s="61"/>
+      <c r="M41" s="61"/>
+      <c r="N41" s="61"/>
+      <c r="O41" s="61"/>
+      <c r="P41" s="61"/>
+      <c r="Q41" s="61"/>
+      <c r="R41" s="61"/>
+      <c r="S41" s="61"/>
+      <c r="T41" s="62"/>
     </row>
     <row r="42" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A42" s="61"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="59"/>
-      <c r="H42" s="59"/>
-      <c r="I42" s="59"/>
-      <c r="J42" s="59"/>
-      <c r="K42" s="59"/>
-      <c r="L42" s="59"/>
-      <c r="M42" s="59"/>
-      <c r="N42" s="59"/>
-      <c r="O42" s="59"/>
-      <c r="P42" s="59"/>
-      <c r="Q42" s="59"/>
-      <c r="R42" s="59"/>
-      <c r="S42" s="59"/>
-      <c r="T42" s="60"/>
+      <c r="A42" s="63"/>
+      <c r="B42" s="60"/>
+      <c r="C42" s="61"/>
+      <c r="D42" s="61"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="61"/>
+      <c r="J42" s="61"/>
+      <c r="K42" s="61"/>
+      <c r="L42" s="61"/>
+      <c r="M42" s="61"/>
+      <c r="N42" s="61"/>
+      <c r="O42" s="61"/>
+      <c r="P42" s="61"/>
+      <c r="Q42" s="61"/>
+      <c r="R42" s="61"/>
+      <c r="S42" s="61"/>
+      <c r="T42" s="62"/>
     </row>
     <row r="43" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A43" s="61"/>
-      <c r="B43" s="58">
+      <c r="A43" s="63"/>
+      <c r="B43" s="60">
         <v>26</v>
       </c>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="59"/>
-      <c r="J43" s="59"/>
-      <c r="K43" s="59"/>
-      <c r="L43" s="59"/>
-      <c r="M43" s="59"/>
-      <c r="N43" s="59"/>
-      <c r="O43" s="59"/>
-      <c r="P43" s="59"/>
-      <c r="Q43" s="59"/>
-      <c r="R43" s="59"/>
-      <c r="S43" s="59"/>
-      <c r="T43" s="60"/>
+      <c r="C43" s="61"/>
+      <c r="D43" s="61"/>
+      <c r="E43" s="61"/>
+      <c r="F43" s="61"/>
+      <c r="G43" s="61"/>
+      <c r="H43" s="61"/>
+      <c r="I43" s="61"/>
+      <c r="J43" s="61"/>
+      <c r="K43" s="61"/>
+      <c r="L43" s="61"/>
+      <c r="M43" s="61"/>
+      <c r="N43" s="61"/>
+      <c r="O43" s="61"/>
+      <c r="P43" s="61"/>
+      <c r="Q43" s="61"/>
+      <c r="R43" s="61"/>
+      <c r="S43" s="61"/>
+      <c r="T43" s="62"/>
     </row>
     <row r="44" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A44" s="61"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="59"/>
-      <c r="D44" s="59"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="59"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="59"/>
-      <c r="J44" s="59"/>
-      <c r="K44" s="59"/>
-      <c r="L44" s="59"/>
-      <c r="M44" s="59"/>
-      <c r="N44" s="59"/>
-      <c r="O44" s="59"/>
-      <c r="P44" s="59"/>
-      <c r="Q44" s="59"/>
-      <c r="R44" s="59"/>
-      <c r="S44" s="59"/>
-      <c r="T44" s="60"/>
+      <c r="A44" s="63"/>
+      <c r="B44" s="60"/>
+      <c r="C44" s="61"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="61"/>
+      <c r="F44" s="61"/>
+      <c r="G44" s="61"/>
+      <c r="H44" s="61"/>
+      <c r="I44" s="61"/>
+      <c r="J44" s="61"/>
+      <c r="K44" s="61"/>
+      <c r="L44" s="61"/>
+      <c r="M44" s="61"/>
+      <c r="N44" s="61"/>
+      <c r="O44" s="61"/>
+      <c r="P44" s="61"/>
+      <c r="Q44" s="61"/>
+      <c r="R44" s="61"/>
+      <c r="S44" s="61"/>
+      <c r="T44" s="62"/>
     </row>
     <row r="45" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A45" s="61"/>
-      <c r="B45" s="58">
+      <c r="A45" s="63"/>
+      <c r="B45" s="60">
         <v>28</v>
       </c>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="59"/>
-      <c r="I45" s="59"/>
-      <c r="J45" s="59"/>
-      <c r="K45" s="59"/>
-      <c r="L45" s="59"/>
-      <c r="M45" s="59"/>
-      <c r="N45" s="59"/>
-      <c r="O45" s="59"/>
-      <c r="P45" s="59"/>
-      <c r="Q45" s="59"/>
-      <c r="R45" s="59"/>
-      <c r="S45" s="59"/>
-      <c r="T45" s="60"/>
+      <c r="C45" s="61"/>
+      <c r="D45" s="61"/>
+      <c r="E45" s="61"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="61"/>
+      <c r="H45" s="61"/>
+      <c r="I45" s="61"/>
+      <c r="J45" s="61"/>
+      <c r="K45" s="61"/>
+      <c r="L45" s="61"/>
+      <c r="M45" s="61"/>
+      <c r="N45" s="61"/>
+      <c r="O45" s="61"/>
+      <c r="P45" s="61"/>
+      <c r="Q45" s="61"/>
+      <c r="R45" s="61"/>
+      <c r="S45" s="61"/>
+      <c r="T45" s="62"/>
     </row>
     <row r="46" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A46" s="61"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="59"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="59"/>
-      <c r="F46" s="59"/>
-      <c r="G46" s="59"/>
-      <c r="H46" s="59"/>
-      <c r="I46" s="59"/>
-      <c r="J46" s="59"/>
-      <c r="K46" s="59"/>
-      <c r="L46" s="59"/>
-      <c r="M46" s="59"/>
-      <c r="N46" s="59"/>
-      <c r="O46" s="59"/>
-      <c r="P46" s="59"/>
-      <c r="Q46" s="59"/>
-      <c r="R46" s="59"/>
-      <c r="S46" s="59"/>
-      <c r="T46" s="60"/>
+      <c r="A46" s="63"/>
+      <c r="B46" s="60"/>
+      <c r="C46" s="61"/>
+      <c r="D46" s="61"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="61"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="61"/>
+      <c r="I46" s="61"/>
+      <c r="J46" s="61"/>
+      <c r="K46" s="61"/>
+      <c r="L46" s="61"/>
+      <c r="M46" s="61"/>
+      <c r="N46" s="61"/>
+      <c r="O46" s="61"/>
+      <c r="P46" s="61"/>
+      <c r="Q46" s="61"/>
+      <c r="R46" s="61"/>
+      <c r="S46" s="61"/>
+      <c r="T46" s="62"/>
     </row>
     <row r="47" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A47" s="61"/>
-      <c r="B47" s="58">
+      <c r="A47" s="63"/>
+      <c r="B47" s="60">
         <v>30</v>
       </c>
-      <c r="C47" s="59"/>
-      <c r="D47" s="59"/>
-      <c r="E47" s="59"/>
-      <c r="F47" s="59"/>
-      <c r="G47" s="59"/>
-      <c r="H47" s="59"/>
-      <c r="I47" s="59"/>
-      <c r="J47" s="59"/>
-      <c r="K47" s="59"/>
-      <c r="L47" s="59"/>
-      <c r="M47" s="59"/>
-      <c r="N47" s="59"/>
-      <c r="O47" s="59"/>
-      <c r="P47" s="59"/>
-      <c r="Q47" s="59"/>
-      <c r="R47" s="59"/>
-      <c r="S47" s="59"/>
-      <c r="T47" s="60"/>
+      <c r="C47" s="61"/>
+      <c r="D47" s="61"/>
+      <c r="E47" s="61"/>
+      <c r="F47" s="61"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="61"/>
+      <c r="I47" s="61"/>
+      <c r="J47" s="61"/>
+      <c r="K47" s="61"/>
+      <c r="L47" s="61"/>
+      <c r="M47" s="61"/>
+      <c r="N47" s="61"/>
+      <c r="O47" s="61"/>
+      <c r="P47" s="61"/>
+      <c r="Q47" s="61"/>
+      <c r="R47" s="61"/>
+      <c r="S47" s="61"/>
+      <c r="T47" s="62"/>
     </row>
     <row r="48" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A48" s="61"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="59"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="59"/>
-      <c r="F48" s="59"/>
-      <c r="G48" s="59"/>
-      <c r="H48" s="59"/>
-      <c r="I48" s="59"/>
-      <c r="J48" s="59"/>
-      <c r="K48" s="59"/>
-      <c r="L48" s="59"/>
-      <c r="M48" s="59"/>
-      <c r="N48" s="59"/>
-      <c r="O48" s="59"/>
-      <c r="P48" s="59"/>
-      <c r="Q48" s="59"/>
-      <c r="R48" s="59"/>
-      <c r="S48" s="59"/>
-      <c r="T48" s="60"/>
+      <c r="A48" s="63"/>
+      <c r="B48" s="60"/>
+      <c r="C48" s="61"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="61"/>
+      <c r="F48" s="61"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="61"/>
+      <c r="I48" s="61"/>
+      <c r="J48" s="61"/>
+      <c r="K48" s="61"/>
+      <c r="L48" s="61"/>
+      <c r="M48" s="61"/>
+      <c r="N48" s="61"/>
+      <c r="O48" s="61"/>
+      <c r="P48" s="61"/>
+      <c r="Q48" s="61"/>
+      <c r="R48" s="61"/>
+      <c r="S48" s="61"/>
+      <c r="T48" s="62"/>
     </row>
     <row r="49" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A49" s="61"/>
-      <c r="B49" s="58">
+      <c r="A49" s="63"/>
+      <c r="B49" s="60">
         <v>32</v>
       </c>
-      <c r="C49" s="59"/>
-      <c r="D49" s="59"/>
-      <c r="E49" s="59"/>
-      <c r="F49" s="59"/>
-      <c r="G49" s="59"/>
-      <c r="H49" s="59"/>
-      <c r="I49" s="59"/>
-      <c r="J49" s="59"/>
-      <c r="K49" s="59"/>
-      <c r="L49" s="59"/>
-      <c r="M49" s="59"/>
-      <c r="N49" s="59"/>
-      <c r="O49" s="59"/>
-      <c r="P49" s="59"/>
-      <c r="Q49" s="59"/>
-      <c r="R49" s="59"/>
-      <c r="S49" s="59"/>
-      <c r="T49" s="60"/>
+      <c r="C49" s="61"/>
+      <c r="D49" s="61"/>
+      <c r="E49" s="61"/>
+      <c r="F49" s="61"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="61"/>
+      <c r="J49" s="61"/>
+      <c r="K49" s="61"/>
+      <c r="L49" s="61"/>
+      <c r="M49" s="61"/>
+      <c r="N49" s="61"/>
+      <c r="O49" s="61"/>
+      <c r="P49" s="61"/>
+      <c r="Q49" s="61"/>
+      <c r="R49" s="61"/>
+      <c r="S49" s="61"/>
+      <c r="T49" s="62"/>
     </row>
     <row r="50" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A50" s="61"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="59"/>
-      <c r="D50" s="59"/>
-      <c r="E50" s="59"/>
-      <c r="F50" s="59"/>
-      <c r="G50" s="59"/>
-      <c r="H50" s="59"/>
-      <c r="I50" s="59"/>
-      <c r="J50" s="59"/>
-      <c r="K50" s="59"/>
-      <c r="L50" s="59"/>
-      <c r="M50" s="59"/>
-      <c r="N50" s="59"/>
-      <c r="O50" s="59"/>
-      <c r="P50" s="59"/>
-      <c r="Q50" s="59"/>
-      <c r="R50" s="59"/>
-      <c r="S50" s="59"/>
-      <c r="T50" s="60"/>
+      <c r="A50" s="63"/>
+      <c r="B50" s="60"/>
+      <c r="C50" s="61"/>
+      <c r="D50" s="61"/>
+      <c r="E50" s="61"/>
+      <c r="F50" s="61"/>
+      <c r="G50" s="61"/>
+      <c r="H50" s="61"/>
+      <c r="I50" s="61"/>
+      <c r="J50" s="61"/>
+      <c r="K50" s="61"/>
+      <c r="L50" s="61"/>
+      <c r="M50" s="61"/>
+      <c r="N50" s="61"/>
+      <c r="O50" s="61"/>
+      <c r="P50" s="61"/>
+      <c r="Q50" s="61"/>
+      <c r="R50" s="61"/>
+      <c r="S50" s="61"/>
+      <c r="T50" s="62"/>
     </row>
     <row r="51" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A51" s="61"/>
-      <c r="B51" s="58">
+      <c r="A51" s="63"/>
+      <c r="B51" s="60">
         <v>34</v>
       </c>
-      <c r="C51" s="59"/>
-      <c r="D51" s="59"/>
-      <c r="E51" s="59"/>
-      <c r="F51" s="59"/>
-      <c r="G51" s="59"/>
-      <c r="H51" s="59"/>
-      <c r="I51" s="59"/>
-      <c r="J51" s="59"/>
-      <c r="K51" s="59"/>
-      <c r="L51" s="59"/>
-      <c r="M51" s="59"/>
-      <c r="N51" s="59"/>
-      <c r="O51" s="59"/>
-      <c r="P51" s="59"/>
-      <c r="Q51" s="59"/>
-      <c r="R51" s="59"/>
-      <c r="S51" s="59"/>
-      <c r="T51" s="60"/>
+      <c r="C51" s="61"/>
+      <c r="D51" s="61"/>
+      <c r="E51" s="61"/>
+      <c r="F51" s="61"/>
+      <c r="G51" s="61"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="61"/>
+      <c r="J51" s="61"/>
+      <c r="K51" s="61"/>
+      <c r="L51" s="61"/>
+      <c r="M51" s="61"/>
+      <c r="N51" s="61"/>
+      <c r="O51" s="61"/>
+      <c r="P51" s="61"/>
+      <c r="Q51" s="61"/>
+      <c r="R51" s="61"/>
+      <c r="S51" s="61"/>
+      <c r="T51" s="62"/>
     </row>
     <row r="52" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A52" s="61"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="59"/>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="59"/>
-      <c r="I52" s="59"/>
-      <c r="J52" s="59"/>
-      <c r="K52" s="59"/>
-      <c r="L52" s="59"/>
-      <c r="M52" s="59"/>
-      <c r="N52" s="59"/>
-      <c r="O52" s="59"/>
-      <c r="P52" s="59"/>
-      <c r="Q52" s="59"/>
-      <c r="R52" s="59"/>
-      <c r="S52" s="59"/>
-      <c r="T52" s="60"/>
+      <c r="A52" s="63"/>
+      <c r="B52" s="60"/>
+      <c r="C52" s="61"/>
+      <c r="D52" s="61"/>
+      <c r="E52" s="61"/>
+      <c r="F52" s="61"/>
+      <c r="G52" s="61"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="61"/>
+      <c r="J52" s="61"/>
+      <c r="K52" s="61"/>
+      <c r="L52" s="61"/>
+      <c r="M52" s="61"/>
+      <c r="N52" s="61"/>
+      <c r="O52" s="61"/>
+      <c r="P52" s="61"/>
+      <c r="Q52" s="61"/>
+      <c r="R52" s="61"/>
+      <c r="S52" s="61"/>
+      <c r="T52" s="62"/>
     </row>
     <row r="53" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A53" s="61"/>
-      <c r="B53" s="58">
+      <c r="A53" s="63"/>
+      <c r="B53" s="60">
         <v>36</v>
       </c>
-      <c r="C53" s="59"/>
-      <c r="D53" s="59"/>
-      <c r="E53" s="59"/>
-      <c r="F53" s="59"/>
-      <c r="G53" s="59"/>
-      <c r="H53" s="59"/>
-      <c r="I53" s="59"/>
-      <c r="J53" s="59"/>
-      <c r="K53" s="59"/>
-      <c r="L53" s="59"/>
-      <c r="M53" s="59"/>
-      <c r="N53" s="59"/>
-      <c r="O53" s="59"/>
-      <c r="P53" s="59"/>
-      <c r="Q53" s="59"/>
-      <c r="R53" s="59"/>
-      <c r="S53" s="59"/>
-      <c r="T53" s="60"/>
+      <c r="C53" s="61"/>
+      <c r="D53" s="61"/>
+      <c r="E53" s="61"/>
+      <c r="F53" s="61"/>
+      <c r="G53" s="61"/>
+      <c r="H53" s="61"/>
+      <c r="I53" s="61"/>
+      <c r="J53" s="61"/>
+      <c r="K53" s="61"/>
+      <c r="L53" s="61"/>
+      <c r="M53" s="61"/>
+      <c r="N53" s="61"/>
+      <c r="O53" s="61"/>
+      <c r="P53" s="61"/>
+      <c r="Q53" s="61"/>
+      <c r="R53" s="61"/>
+      <c r="S53" s="61"/>
+      <c r="T53" s="62"/>
     </row>
     <row r="54" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A54" s="61"/>
-      <c r="B54" s="58"/>
-      <c r="C54" s="59"/>
-      <c r="D54" s="59"/>
-      <c r="E54" s="59"/>
-      <c r="F54" s="59"/>
-      <c r="G54" s="59"/>
-      <c r="H54" s="59"/>
-      <c r="I54" s="59"/>
-      <c r="J54" s="59"/>
-      <c r="K54" s="59"/>
-      <c r="L54" s="59"/>
-      <c r="M54" s="59"/>
-      <c r="N54" s="59"/>
-      <c r="O54" s="59"/>
-      <c r="P54" s="59"/>
-      <c r="Q54" s="59"/>
-      <c r="R54" s="59"/>
-      <c r="S54" s="59"/>
-      <c r="T54" s="60"/>
+      <c r="A54" s="63"/>
+      <c r="B54" s="60"/>
+      <c r="C54" s="61"/>
+      <c r="D54" s="61"/>
+      <c r="E54" s="61"/>
+      <c r="F54" s="61"/>
+      <c r="G54" s="61"/>
+      <c r="H54" s="61"/>
+      <c r="I54" s="61"/>
+      <c r="J54" s="61"/>
+      <c r="K54" s="61"/>
+      <c r="L54" s="61"/>
+      <c r="M54" s="61"/>
+      <c r="N54" s="61"/>
+      <c r="O54" s="61"/>
+      <c r="P54" s="61"/>
+      <c r="Q54" s="61"/>
+      <c r="R54" s="61"/>
+      <c r="S54" s="61"/>
+      <c r="T54" s="62"/>
     </row>
     <row r="55" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A55" s="61"/>
-      <c r="B55" s="58">
+      <c r="A55" s="63"/>
+      <c r="B55" s="60">
         <v>38</v>
       </c>
-      <c r="C55" s="59"/>
-      <c r="D55" s="59"/>
-      <c r="E55" s="59"/>
-      <c r="F55" s="59"/>
-      <c r="G55" s="59"/>
-      <c r="H55" s="59"/>
-      <c r="I55" s="59"/>
-      <c r="J55" s="59"/>
-      <c r="K55" s="59"/>
-      <c r="L55" s="59"/>
-      <c r="M55" s="59"/>
-      <c r="N55" s="59"/>
-      <c r="O55" s="59"/>
-      <c r="P55" s="59"/>
-      <c r="Q55" s="59"/>
-      <c r="R55" s="59"/>
-      <c r="S55" s="59"/>
-      <c r="T55" s="60"/>
+      <c r="C55" s="61"/>
+      <c r="D55" s="61"/>
+      <c r="E55" s="61"/>
+      <c r="F55" s="61"/>
+      <c r="G55" s="61"/>
+      <c r="H55" s="61"/>
+      <c r="I55" s="61"/>
+      <c r="J55" s="61"/>
+      <c r="K55" s="61"/>
+      <c r="L55" s="61"/>
+      <c r="M55" s="61"/>
+      <c r="N55" s="61"/>
+      <c r="O55" s="61"/>
+      <c r="P55" s="61"/>
+      <c r="Q55" s="61"/>
+      <c r="R55" s="61"/>
+      <c r="S55" s="61"/>
+      <c r="T55" s="62"/>
     </row>
     <row r="56" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A56" s="61"/>
-      <c r="B56" s="58"/>
-      <c r="C56" s="59"/>
-      <c r="D56" s="59"/>
-      <c r="E56" s="59"/>
-      <c r="F56" s="59"/>
-      <c r="G56" s="59"/>
-      <c r="H56" s="59"/>
-      <c r="I56" s="59"/>
-      <c r="J56" s="59"/>
-      <c r="K56" s="59"/>
-      <c r="L56" s="59"/>
-      <c r="M56" s="59"/>
-      <c r="N56" s="59"/>
-      <c r="O56" s="59"/>
-      <c r="P56" s="59"/>
-      <c r="Q56" s="59"/>
-      <c r="R56" s="59"/>
-      <c r="S56" s="59"/>
-      <c r="T56" s="60"/>
+      <c r="A56" s="63"/>
+      <c r="B56" s="60"/>
+      <c r="C56" s="61"/>
+      <c r="D56" s="61"/>
+      <c r="E56" s="61"/>
+      <c r="F56" s="61"/>
+      <c r="G56" s="61"/>
+      <c r="H56" s="61"/>
+      <c r="I56" s="61"/>
+      <c r="J56" s="61"/>
+      <c r="K56" s="61"/>
+      <c r="L56" s="61"/>
+      <c r="M56" s="61"/>
+      <c r="N56" s="61"/>
+      <c r="O56" s="61"/>
+      <c r="P56" s="61"/>
+      <c r="Q56" s="61"/>
+      <c r="R56" s="61"/>
+      <c r="S56" s="61"/>
+      <c r="T56" s="62"/>
     </row>
     <row r="57" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A57" s="61"/>
-      <c r="B57" s="58">
+      <c r="A57" s="63"/>
+      <c r="B57" s="60">
         <v>40</v>
       </c>
-      <c r="C57" s="59"/>
-      <c r="D57" s="59"/>
-      <c r="E57" s="59"/>
-      <c r="F57" s="59"/>
-      <c r="G57" s="59"/>
-      <c r="H57" s="59"/>
-      <c r="I57" s="59"/>
-      <c r="J57" s="59"/>
-      <c r="K57" s="59"/>
-      <c r="L57" s="59"/>
-      <c r="M57" s="59"/>
-      <c r="N57" s="59"/>
-      <c r="O57" s="59"/>
-      <c r="P57" s="59"/>
-      <c r="Q57" s="59"/>
-      <c r="R57" s="59"/>
-      <c r="S57" s="59"/>
-      <c r="T57" s="60"/>
+      <c r="C57" s="61"/>
+      <c r="D57" s="61"/>
+      <c r="E57" s="61"/>
+      <c r="F57" s="61"/>
+      <c r="G57" s="61"/>
+      <c r="H57" s="61"/>
+      <c r="I57" s="61"/>
+      <c r="J57" s="61"/>
+      <c r="K57" s="61"/>
+      <c r="L57" s="61"/>
+      <c r="M57" s="61"/>
+      <c r="N57" s="61"/>
+      <c r="O57" s="61"/>
+      <c r="P57" s="61"/>
+      <c r="Q57" s="61"/>
+      <c r="R57" s="61"/>
+      <c r="S57" s="61"/>
+      <c r="T57" s="62"/>
     </row>
     <row r="58" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A58" s="61"/>
-      <c r="B58" s="58"/>
-      <c r="C58" s="59"/>
-      <c r="D58" s="59"/>
-      <c r="E58" s="59"/>
-      <c r="F58" s="59"/>
-      <c r="G58" s="59"/>
-      <c r="H58" s="59"/>
-      <c r="I58" s="59"/>
-      <c r="J58" s="59"/>
-      <c r="K58" s="59"/>
-      <c r="L58" s="59"/>
-      <c r="M58" s="59"/>
-      <c r="N58" s="59"/>
-      <c r="O58" s="59"/>
-      <c r="P58" s="59"/>
-      <c r="Q58" s="59"/>
-      <c r="R58" s="59"/>
-      <c r="S58" s="59"/>
-      <c r="T58" s="60"/>
+      <c r="A58" s="63"/>
+      <c r="B58" s="60"/>
+      <c r="C58" s="61"/>
+      <c r="D58" s="61"/>
+      <c r="E58" s="61"/>
+      <c r="F58" s="61"/>
+      <c r="G58" s="61"/>
+      <c r="H58" s="61"/>
+      <c r="I58" s="61"/>
+      <c r="J58" s="61"/>
+      <c r="K58" s="61"/>
+      <c r="L58" s="61"/>
+      <c r="M58" s="61"/>
+      <c r="N58" s="61"/>
+      <c r="O58" s="61"/>
+      <c r="P58" s="61"/>
+      <c r="Q58" s="61"/>
+      <c r="R58" s="61"/>
+      <c r="S58" s="61"/>
+      <c r="T58" s="62"/>
     </row>
     <row r="59" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A59" s="61"/>
-      <c r="B59" s="58">
+      <c r="A59" s="63"/>
+      <c r="B59" s="60">
         <v>42</v>
       </c>
-      <c r="C59" s="59"/>
-      <c r="D59" s="59"/>
-      <c r="E59" s="59"/>
-      <c r="F59" s="59"/>
-      <c r="G59" s="59"/>
-      <c r="H59" s="59"/>
-      <c r="I59" s="59"/>
-      <c r="J59" s="59"/>
-      <c r="K59" s="59"/>
-      <c r="L59" s="59"/>
-      <c r="M59" s="59"/>
-      <c r="N59" s="59"/>
-      <c r="O59" s="59"/>
-      <c r="P59" s="59"/>
-      <c r="Q59" s="59"/>
-      <c r="R59" s="59"/>
-      <c r="S59" s="59"/>
-      <c r="T59" s="60"/>
+      <c r="C59" s="61"/>
+      <c r="D59" s="61"/>
+      <c r="E59" s="61"/>
+      <c r="F59" s="61"/>
+      <c r="G59" s="61"/>
+      <c r="H59" s="61"/>
+      <c r="I59" s="61"/>
+      <c r="J59" s="61"/>
+      <c r="K59" s="61"/>
+      <c r="L59" s="61"/>
+      <c r="M59" s="61"/>
+      <c r="N59" s="61"/>
+      <c r="O59" s="61"/>
+      <c r="P59" s="61"/>
+      <c r="Q59" s="61"/>
+      <c r="R59" s="61"/>
+      <c r="S59" s="61"/>
+      <c r="T59" s="62"/>
     </row>
     <row r="60" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A60" s="61"/>
-      <c r="B60" s="58"/>
-      <c r="C60" s="59"/>
-      <c r="D60" s="59"/>
-      <c r="E60" s="59"/>
-      <c r="F60" s="59"/>
-      <c r="G60" s="59"/>
-      <c r="H60" s="59"/>
-      <c r="I60" s="59"/>
-      <c r="J60" s="59"/>
-      <c r="K60" s="59"/>
-      <c r="L60" s="59"/>
-      <c r="M60" s="59"/>
-      <c r="N60" s="59"/>
-      <c r="O60" s="59"/>
-      <c r="P60" s="59"/>
-      <c r="Q60" s="59"/>
-      <c r="R60" s="59"/>
-      <c r="S60" s="59"/>
-      <c r="T60" s="60"/>
+      <c r="A60" s="63"/>
+      <c r="B60" s="60"/>
+      <c r="C60" s="61"/>
+      <c r="D60" s="61"/>
+      <c r="E60" s="61"/>
+      <c r="F60" s="61"/>
+      <c r="G60" s="61"/>
+      <c r="H60" s="61"/>
+      <c r="I60" s="61"/>
+      <c r="J60" s="61"/>
+      <c r="K60" s="61"/>
+      <c r="L60" s="61"/>
+      <c r="M60" s="61"/>
+      <c r="N60" s="61"/>
+      <c r="O60" s="61"/>
+      <c r="P60" s="61"/>
+      <c r="Q60" s="61"/>
+      <c r="R60" s="61"/>
+      <c r="S60" s="61"/>
+      <c r="T60" s="62"/>
     </row>
     <row r="61" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A61" s="61"/>
-      <c r="B61" s="58">
+      <c r="A61" s="63"/>
+      <c r="B61" s="60">
         <v>44</v>
       </c>
-      <c r="C61" s="59"/>
-      <c r="D61" s="59"/>
-      <c r="E61" s="59"/>
-      <c r="F61" s="59"/>
-      <c r="G61" s="59"/>
-      <c r="H61" s="59"/>
-      <c r="I61" s="59"/>
-      <c r="J61" s="59"/>
-      <c r="K61" s="59"/>
-      <c r="L61" s="59"/>
-      <c r="M61" s="59"/>
-      <c r="N61" s="59"/>
-      <c r="O61" s="59"/>
-      <c r="P61" s="59"/>
-      <c r="Q61" s="59"/>
-      <c r="R61" s="59"/>
-      <c r="S61" s="59"/>
-      <c r="T61" s="60"/>
+      <c r="C61" s="61"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
+      <c r="H61" s="61"/>
+      <c r="I61" s="61"/>
+      <c r="J61" s="61"/>
+      <c r="K61" s="61"/>
+      <c r="L61" s="61"/>
+      <c r="M61" s="61"/>
+      <c r="N61" s="61"/>
+      <c r="O61" s="61"/>
+      <c r="P61" s="61"/>
+      <c r="Q61" s="61"/>
+      <c r="R61" s="61"/>
+      <c r="S61" s="61"/>
+      <c r="T61" s="62"/>
     </row>
     <row r="62" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A62" s="61"/>
-      <c r="B62" s="58"/>
-      <c r="C62" s="59"/>
-      <c r="D62" s="59"/>
-      <c r="E62" s="59"/>
-      <c r="F62" s="59"/>
-      <c r="G62" s="59"/>
-      <c r="H62" s="59"/>
-      <c r="I62" s="59"/>
-      <c r="J62" s="59"/>
-      <c r="K62" s="59"/>
-      <c r="L62" s="59"/>
-      <c r="M62" s="59"/>
-      <c r="N62" s="59"/>
-      <c r="O62" s="59"/>
-      <c r="P62" s="59"/>
-      <c r="Q62" s="59"/>
-      <c r="R62" s="59"/>
-      <c r="S62" s="59"/>
-      <c r="T62" s="60"/>
+      <c r="A62" s="63"/>
+      <c r="B62" s="60"/>
+      <c r="C62" s="61"/>
+      <c r="D62" s="61"/>
+      <c r="E62" s="61"/>
+      <c r="F62" s="61"/>
+      <c r="G62" s="61"/>
+      <c r="H62" s="61"/>
+      <c r="I62" s="61"/>
+      <c r="J62" s="61"/>
+      <c r="K62" s="61"/>
+      <c r="L62" s="61"/>
+      <c r="M62" s="61"/>
+      <c r="N62" s="61"/>
+      <c r="O62" s="61"/>
+      <c r="P62" s="61"/>
+      <c r="Q62" s="61"/>
+      <c r="R62" s="61"/>
+      <c r="S62" s="61"/>
+      <c r="T62" s="62"/>
     </row>
     <row r="63" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A63" s="61"/>
-      <c r="B63" s="58">
+      <c r="A63" s="63"/>
+      <c r="B63" s="60">
         <v>46</v>
       </c>
-      <c r="C63" s="59"/>
-      <c r="D63" s="59"/>
-      <c r="E63" s="59"/>
-      <c r="F63" s="59"/>
-      <c r="G63" s="59"/>
-      <c r="H63" s="59"/>
-      <c r="I63" s="59"/>
-      <c r="J63" s="59"/>
-      <c r="K63" s="59"/>
-      <c r="L63" s="59"/>
-      <c r="M63" s="59"/>
-      <c r="N63" s="59"/>
-      <c r="O63" s="59"/>
-      <c r="P63" s="59"/>
-      <c r="Q63" s="59"/>
-      <c r="R63" s="59"/>
-      <c r="S63" s="59"/>
-      <c r="T63" s="60"/>
+      <c r="C63" s="61"/>
+      <c r="D63" s="61"/>
+      <c r="E63" s="61"/>
+      <c r="F63" s="61"/>
+      <c r="G63" s="61"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61"/>
+      <c r="J63" s="61"/>
+      <c r="K63" s="61"/>
+      <c r="L63" s="61"/>
+      <c r="M63" s="61"/>
+      <c r="N63" s="61"/>
+      <c r="O63" s="61"/>
+      <c r="P63" s="61"/>
+      <c r="Q63" s="61"/>
+      <c r="R63" s="61"/>
+      <c r="S63" s="61"/>
+      <c r="T63" s="62"/>
     </row>
     <row r="64" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A64" s="61"/>
-      <c r="B64" s="58"/>
-      <c r="C64" s="59"/>
-      <c r="D64" s="59"/>
-      <c r="E64" s="59"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="59"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="59"/>
-      <c r="J64" s="59"/>
-      <c r="K64" s="59"/>
-      <c r="L64" s="59"/>
-      <c r="M64" s="59"/>
-      <c r="N64" s="59"/>
-      <c r="O64" s="59"/>
-      <c r="P64" s="59"/>
-      <c r="Q64" s="59"/>
-      <c r="R64" s="59"/>
-      <c r="S64" s="59"/>
-      <c r="T64" s="60"/>
+      <c r="A64" s="63"/>
+      <c r="B64" s="60"/>
+      <c r="C64" s="61"/>
+      <c r="D64" s="61"/>
+      <c r="E64" s="61"/>
+      <c r="F64" s="61"/>
+      <c r="G64" s="61"/>
+      <c r="H64" s="61"/>
+      <c r="I64" s="61"/>
+      <c r="J64" s="61"/>
+      <c r="K64" s="61"/>
+      <c r="L64" s="61"/>
+      <c r="M64" s="61"/>
+      <c r="N64" s="61"/>
+      <c r="O64" s="61"/>
+      <c r="P64" s="61"/>
+      <c r="Q64" s="61"/>
+      <c r="R64" s="61"/>
+      <c r="S64" s="61"/>
+      <c r="T64" s="62"/>
     </row>
     <row r="65" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A65" s="61"/>
-      <c r="B65" s="58">
+      <c r="A65" s="63"/>
+      <c r="B65" s="60">
         <v>48</v>
       </c>
-      <c r="C65" s="59"/>
-      <c r="D65" s="59"/>
-      <c r="E65" s="59"/>
-      <c r="F65" s="59"/>
-      <c r="G65" s="59"/>
-      <c r="H65" s="59"/>
-      <c r="I65" s="59"/>
-      <c r="J65" s="59"/>
-      <c r="K65" s="59"/>
-      <c r="L65" s="59"/>
-      <c r="M65" s="59"/>
-      <c r="N65" s="59"/>
-      <c r="O65" s="59"/>
-      <c r="P65" s="59"/>
-      <c r="Q65" s="59"/>
-      <c r="R65" s="59"/>
-      <c r="S65" s="59"/>
-      <c r="T65" s="60"/>
+      <c r="C65" s="61"/>
+      <c r="D65" s="61"/>
+      <c r="E65" s="61"/>
+      <c r="F65" s="61"/>
+      <c r="G65" s="61"/>
+      <c r="H65" s="61"/>
+      <c r="I65" s="61"/>
+      <c r="J65" s="61"/>
+      <c r="K65" s="61"/>
+      <c r="L65" s="61"/>
+      <c r="M65" s="61"/>
+      <c r="N65" s="61"/>
+      <c r="O65" s="61"/>
+      <c r="P65" s="61"/>
+      <c r="Q65" s="61"/>
+      <c r="R65" s="61"/>
+      <c r="S65" s="61"/>
+      <c r="T65" s="62"/>
     </row>
     <row r="66" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A66" s="61"/>
-      <c r="B66" s="58"/>
-      <c r="C66" s="59"/>
-      <c r="D66" s="59"/>
-      <c r="E66" s="59"/>
-      <c r="F66" s="59"/>
-      <c r="G66" s="59"/>
-      <c r="H66" s="59"/>
-      <c r="I66" s="59"/>
-      <c r="J66" s="59"/>
-      <c r="K66" s="59"/>
-      <c r="L66" s="59"/>
-      <c r="M66" s="59"/>
-      <c r="N66" s="59"/>
-      <c r="O66" s="59"/>
-      <c r="P66" s="59"/>
-      <c r="Q66" s="59"/>
-      <c r="R66" s="59"/>
-      <c r="S66" s="59"/>
-      <c r="T66" s="60"/>
+      <c r="A66" s="63"/>
+      <c r="B66" s="60"/>
+      <c r="C66" s="61"/>
+      <c r="D66" s="61"/>
+      <c r="E66" s="61"/>
+      <c r="F66" s="61"/>
+      <c r="G66" s="61"/>
+      <c r="H66" s="61"/>
+      <c r="I66" s="61"/>
+      <c r="J66" s="61"/>
+      <c r="K66" s="61"/>
+      <c r="L66" s="61"/>
+      <c r="M66" s="61"/>
+      <c r="N66" s="61"/>
+      <c r="O66" s="61"/>
+      <c r="P66" s="61"/>
+      <c r="Q66" s="61"/>
+      <c r="R66" s="61"/>
+      <c r="S66" s="61"/>
+      <c r="T66" s="62"/>
     </row>
     <row r="67" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A67" s="61"/>
-      <c r="B67" s="58">
+      <c r="A67" s="63"/>
+      <c r="B67" s="60">
         <v>50</v>
       </c>
-      <c r="C67" s="59"/>
-      <c r="D67" s="59"/>
-      <c r="E67" s="59"/>
-      <c r="F67" s="59"/>
-      <c r="G67" s="59"/>
-      <c r="H67" s="59"/>
-      <c r="I67" s="59"/>
-      <c r="J67" s="59"/>
-      <c r="K67" s="59"/>
-      <c r="L67" s="59"/>
-      <c r="M67" s="59"/>
-      <c r="N67" s="59"/>
-      <c r="O67" s="59"/>
-      <c r="P67" s="59"/>
-      <c r="Q67" s="59"/>
-      <c r="R67" s="59"/>
-      <c r="S67" s="59"/>
-      <c r="T67" s="60"/>
+      <c r="C67" s="61"/>
+      <c r="D67" s="61"/>
+      <c r="E67" s="61"/>
+      <c r="F67" s="61"/>
+      <c r="G67" s="61"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="61"/>
+      <c r="K67" s="61"/>
+      <c r="L67" s="61"/>
+      <c r="M67" s="61"/>
+      <c r="N67" s="61"/>
+      <c r="O67" s="61"/>
+      <c r="P67" s="61"/>
+      <c r="Q67" s="61"/>
+      <c r="R67" s="61"/>
+      <c r="S67" s="61"/>
+      <c r="T67" s="62"/>
     </row>
     <row r="68" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A68" s="61"/>
-      <c r="B68" s="58"/>
-      <c r="C68" s="59"/>
-      <c r="D68" s="59"/>
-      <c r="E68" s="59"/>
-      <c r="F68" s="59"/>
-      <c r="G68" s="59"/>
+      <c r="A68" s="63"/>
+      <c r="B68" s="60"/>
+      <c r="C68" s="61"/>
+      <c r="D68" s="61"/>
+      <c r="E68" s="61"/>
+      <c r="F68" s="61"/>
+      <c r="G68" s="61"/>
       <c r="H68"/>
-      <c r="I68" s="59"/>
+      <c r="I68" s="61"/>
       <c r="J68"/>
-      <c r="K68" s="59"/>
-      <c r="L68" s="59"/>
-      <c r="M68" s="59"/>
-      <c r="N68" s="59"/>
-      <c r="O68" s="59"/>
-      <c r="P68" s="59"/>
-      <c r="Q68" s="59"/>
-      <c r="R68" s="59"/>
-      <c r="S68" s="59"/>
-      <c r="T68" s="60"/>
+      <c r="K68" s="61"/>
+      <c r="L68" s="61"/>
+      <c r="M68" s="61"/>
+      <c r="N68" s="61"/>
+      <c r="O68" s="61"/>
+      <c r="P68" s="61"/>
+      <c r="Q68" s="61"/>
+      <c r="R68" s="61"/>
+      <c r="S68" s="61"/>
+      <c r="T68" s="62"/>
     </row>
     <row r="69" s="2" customFormat="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A69" s="61"/>
-      <c r="B69" s="58">
+      <c r="A69" s="63"/>
+      <c r="B69" s="60">
         <v>52</v>
       </c>
-      <c r="C69" s="59"/>
-      <c r="D69" s="59"/>
-      <c r="E69" s="59"/>
-      <c r="F69" s="59"/>
-      <c r="G69" s="59"/>
-      <c r="H69" s="59"/>
-      <c r="I69" s="59"/>
+      <c r="C69" s="61"/>
+      <c r="D69" s="61"/>
+      <c r="E69" s="61"/>
+      <c r="F69" s="61"/>
+      <c r="G69" s="61"/>
+      <c r="H69" s="61"/>
+      <c r="I69" s="61"/>
       <c r="J69"/>
-      <c r="K69" s="59"/>
-      <c r="L69" s="59"/>
-      <c r="M69" s="59"/>
-      <c r="N69" s="59"/>
-      <c r="O69" s="59"/>
-      <c r="P69" s="59"/>
-      <c r="Q69" s="59"/>
-      <c r="R69" s="59"/>
-      <c r="S69" s="59"/>
-      <c r="T69" s="60"/>
+      <c r="K69" s="61"/>
+      <c r="L69" s="61"/>
+      <c r="M69" s="61"/>
+      <c r="N69" s="61"/>
+      <c r="O69" s="61"/>
+      <c r="P69" s="61"/>
+      <c r="Q69" s="61"/>
+      <c r="R69" s="61"/>
+      <c r="S69" s="61"/>
+      <c r="T69" s="62"/>
     </row>
     <row r="70" s="1" customFormat="1" ht="29.1" customHeight="1" spans="1:20">
-      <c r="A70" s="62" t="s">
+      <c r="A70" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="B70" s="63"/>
-      <c r="C70" s="63"/>
-      <c r="D70" s="64"/>
-      <c r="E70" s="65"/>
-      <c r="F70" s="66"/>
-      <c r="G70" s="67"/>
-      <c r="H70" s="68"/>
-      <c r="I70" s="69"/>
-      <c r="J70" s="70"/>
-      <c r="K70" s="70"/>
-      <c r="L70" s="71"/>
-      <c r="M70" s="67"/>
-      <c r="N70" s="68"/>
-      <c r="O70" s="69"/>
-      <c r="P70" s="70"/>
-      <c r="Q70" s="70"/>
-      <c r="R70" s="71"/>
-      <c r="S70" s="67"/>
-      <c r="T70" s="72"/>
+      <c r="B70" s="65"/>
+      <c r="C70" s="65"/>
+      <c r="D70" s="66"/>
+      <c r="E70" s="67"/>
+      <c r="F70" s="68"/>
+      <c r="G70" s="69"/>
+      <c r="H70" s="70"/>
+      <c r="I70" s="71"/>
+      <c r="J70" s="72"/>
+      <c r="K70" s="72"/>
+      <c r="L70" s="73"/>
+      <c r="M70" s="69"/>
+      <c r="N70" s="70"/>
+      <c r="O70" s="71"/>
+      <c r="P70" s="72"/>
+      <c r="Q70" s="72"/>
+      <c r="R70" s="73"/>
+      <c r="S70" s="69"/>
+      <c r="T70" s="74"/>
     </row>
     <row r="71" s="1" customFormat="1" ht="29.1" customHeight="1" spans="1:20">
-      <c r="A71" s="62" t="s">
+      <c r="A71" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="B71" s="63"/>
-      <c r="C71" s="63"/>
-      <c r="D71" s="64"/>
-      <c r="E71" s="65"/>
-      <c r="F71" s="66"/>
-      <c r="G71" s="73"/>
-      <c r="H71" s="74"/>
-      <c r="I71" s="69"/>
-      <c r="J71" s="70"/>
-      <c r="K71" s="70"/>
-      <c r="L71" s="71"/>
-      <c r="M71" s="73"/>
-      <c r="N71" s="74"/>
-      <c r="O71" s="69"/>
-      <c r="P71" s="70"/>
-      <c r="Q71" s="70"/>
-      <c r="R71" s="71"/>
-      <c r="S71" s="73"/>
-      <c r="T71" s="75"/>
+      <c r="B71" s="65"/>
+      <c r="C71" s="65"/>
+      <c r="D71" s="66"/>
+      <c r="E71" s="67"/>
+      <c r="F71" s="68"/>
+      <c r="G71" s="75"/>
+      <c r="H71" s="76"/>
+      <c r="I71" s="71"/>
+      <c r="J71" s="72"/>
+      <c r="K71" s="72"/>
+      <c r="L71" s="73"/>
+      <c r="M71" s="75"/>
+      <c r="N71" s="76"/>
+      <c r="O71" s="71"/>
+      <c r="P71" s="72"/>
+      <c r="Q71" s="72"/>
+      <c r="R71" s="73"/>
+      <c r="S71" s="75"/>
+      <c r="T71" s="77"/>
     </row>
     <row r="72" s="1" customFormat="1" ht="29.1" customHeight="1" spans="1:20">
-      <c r="A72" s="62" t="s">
+      <c r="A72" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="B72" s="63"/>
-      <c r="C72" s="63"/>
-      <c r="D72" s="69"/>
-      <c r="E72" s="70"/>
-      <c r="F72" s="71"/>
-      <c r="G72" s="73"/>
-      <c r="H72" s="74"/>
-      <c r="I72" s="69"/>
-      <c r="J72" s="70"/>
-      <c r="K72" s="70"/>
-      <c r="L72" s="71"/>
-      <c r="M72" s="73"/>
-      <c r="N72" s="74"/>
-      <c r="O72" s="69"/>
-      <c r="P72" s="70"/>
-      <c r="Q72" s="70"/>
-      <c r="R72" s="71"/>
-      <c r="S72" s="73"/>
-      <c r="T72" s="75"/>
+      <c r="B72" s="65"/>
+      <c r="C72" s="65"/>
+      <c r="D72" s="71"/>
+      <c r="E72" s="72"/>
+      <c r="F72" s="73"/>
+      <c r="G72" s="75"/>
+      <c r="H72" s="76"/>
+      <c r="I72" s="71"/>
+      <c r="J72" s="72"/>
+      <c r="K72" s="72"/>
+      <c r="L72" s="73"/>
+      <c r="M72" s="75"/>
+      <c r="N72" s="76"/>
+      <c r="O72" s="71"/>
+      <c r="P72" s="72"/>
+      <c r="Q72" s="72"/>
+      <c r="R72" s="73"/>
+      <c r="S72" s="75"/>
+      <c r="T72" s="77"/>
     </row>
     <row r="73" s="1" customFormat="1" ht="29.1" customHeight="1" spans="1:20">
-      <c r="A73" s="62" t="s">
+      <c r="A73" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="B73" s="76"/>
-      <c r="C73" s="76"/>
-      <c r="D73" s="69"/>
-      <c r="E73" s="70"/>
-      <c r="F73" s="71"/>
-      <c r="G73" s="77"/>
-      <c r="H73" s="78"/>
-      <c r="I73" s="69"/>
-      <c r="J73" s="70"/>
-      <c r="K73" s="70"/>
-      <c r="L73" s="71"/>
-      <c r="M73" s="77"/>
-      <c r="N73" s="78"/>
-      <c r="O73" s="69"/>
-      <c r="P73" s="70"/>
-      <c r="Q73" s="70"/>
-      <c r="R73" s="71"/>
-      <c r="S73" s="77"/>
-      <c r="T73" s="79"/>
+      <c r="B73" s="78"/>
+      <c r="C73" s="78"/>
+      <c r="D73" s="71"/>
+      <c r="E73" s="72"/>
+      <c r="F73" s="73"/>
+      <c r="G73" s="79"/>
+      <c r="H73" s="80"/>
+      <c r="I73" s="71"/>
+      <c r="J73" s="72"/>
+      <c r="K73" s="72"/>
+      <c r="L73" s="73"/>
+      <c r="M73" s="79"/>
+      <c r="N73" s="80"/>
+      <c r="O73" s="71"/>
+      <c r="P73" s="72"/>
+      <c r="Q73" s="72"/>
+      <c r="R73" s="73"/>
+      <c r="S73" s="79"/>
+      <c r="T73" s="81"/>
     </row>
     <row r="74" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:20">
-      <c r="A74" s="80" t="s">
+      <c r="A74" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="B74" s="81"/>
-      <c r="C74" s="81"/>
-      <c r="D74" s="81"/>
-      <c r="E74" s="81"/>
-      <c r="F74" s="81"/>
-      <c r="G74" s="81"/>
-      <c r="H74" s="81"/>
-      <c r="I74" s="81"/>
-      <c r="J74" s="81"/>
-      <c r="K74" s="81"/>
-      <c r="L74" s="81"/>
-      <c r="M74" s="81"/>
-      <c r="N74" s="81"/>
-      <c r="O74" s="81"/>
-      <c r="P74" s="81"/>
-      <c r="Q74" s="81"/>
-      <c r="R74" s="81"/>
-      <c r="S74" s="81"/>
-      <c r="T74" s="82"/>
+      <c r="B74" s="83"/>
+      <c r="C74" s="83"/>
+      <c r="D74" s="83"/>
+      <c r="E74" s="83"/>
+      <c r="F74" s="83"/>
+      <c r="G74" s="83"/>
+      <c r="H74" s="83"/>
+      <c r="I74" s="83"/>
+      <c r="J74" s="83"/>
+      <c r="K74" s="83"/>
+      <c r="L74" s="83"/>
+      <c r="M74" s="83"/>
+      <c r="N74" s="83"/>
+      <c r="O74" s="83"/>
+      <c r="P74" s="83"/>
+      <c r="Q74" s="83"/>
+      <c r="R74" s="83"/>
+      <c r="S74" s="83"/>
+      <c r="T74" s="84"/>
     </row>
     <row r="75" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:20">
-      <c r="A75" s="80" t="s">
+      <c r="A75" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="B75" s="81"/>
-      <c r="C75" s="81"/>
-      <c r="D75" s="81"/>
-      <c r="E75" s="81"/>
-      <c r="F75" s="81"/>
-      <c r="G75" s="81"/>
-      <c r="H75" s="81"/>
-      <c r="I75" s="81" t="s">
+      <c r="B75" s="83"/>
+      <c r="C75" s="83"/>
+      <c r="D75" s="83"/>
+      <c r="E75" s="83"/>
+      <c r="F75" s="83"/>
+      <c r="G75" s="83"/>
+      <c r="H75" s="83"/>
+      <c r="I75" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="J75" s="83"/>
-      <c r="K75" s="83"/>
-      <c r="L75" s="83"/>
-      <c r="M75" s="83"/>
-      <c r="N75" s="83"/>
-      <c r="O75" s="83"/>
-      <c r="P75" s="81" t="s">
+      <c r="J75" s="85"/>
+      <c r="K75" s="85"/>
+      <c r="L75" s="85"/>
+      <c r="M75" s="85"/>
+      <c r="N75" s="85"/>
+      <c r="O75" s="85"/>
+      <c r="P75" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="Q75" s="83"/>
-      <c r="R75" s="83"/>
-      <c r="S75" s="83"/>
-      <c r="T75" s="84"/>
+      <c r="Q75" s="85"/>
+      <c r="R75" s="85"/>
+      <c r="S75" s="85"/>
+      <c r="T75" s="86"/>
     </row>
     <row r="76" s="1" customFormat="1" ht="114.95" customHeight="1" spans="1:20">
-      <c r="A76" s="85"/>
-      <c r="B76" s="86"/>
-      <c r="C76" s="86"/>
-      <c r="D76" s="86"/>
-      <c r="E76" s="86"/>
-      <c r="F76" s="86"/>
-      <c r="G76" s="87"/>
-      <c r="H76" s="88"/>
-      <c r="I76" s="89"/>
-      <c r="J76" s="89"/>
-      <c r="K76" s="89"/>
-      <c r="L76" s="89"/>
-      <c r="M76" s="89"/>
-      <c r="N76" s="89"/>
-      <c r="O76" s="90"/>
-      <c r="P76" s="91"/>
-      <c r="Q76" s="91"/>
-      <c r="R76" s="91"/>
-      <c r="S76" s="91"/>
-      <c r="T76" s="92"/>
+      <c r="A76" s="87"/>
+      <c r="B76" s="88"/>
+      <c r="C76" s="88"/>
+      <c r="D76" s="88"/>
+      <c r="E76" s="88"/>
+      <c r="F76" s="88"/>
+      <c r="G76" s="89"/>
+      <c r="H76" s="90"/>
+      <c r="I76" s="91"/>
+      <c r="J76" s="91"/>
+      <c r="K76" s="91"/>
+      <c r="L76" s="91"/>
+      <c r="M76" s="91"/>
+      <c r="N76" s="91"/>
+      <c r="O76" s="92"/>
+      <c r="P76" s="93"/>
+      <c r="Q76" s="93"/>
+      <c r="R76" s="93"/>
+      <c r="S76" s="93"/>
+      <c r="T76" s="94"/>
     </row>
     <row r="77" ht="30.95" customHeight="1" spans="1:20">
-      <c r="A77" s="93"/>
-      <c r="B77" s="94"/>
-      <c r="C77" s="94"/>
-      <c r="D77" s="95" t="s">
+      <c r="A77" s="95"/>
+      <c r="B77" s="96"/>
+      <c r="C77" s="96"/>
+      <c r="D77" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="E77" s="95"/>
-      <c r="F77" s="96" t="s">
+      <c r="E77" s="97"/>
+      <c r="F77" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="G77" s="95"/>
-      <c r="H77" s="95" t="s">
+      <c r="G77" s="97"/>
+      <c r="H77" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="I77" s="95"/>
-      <c r="J77" s="96" t="s">
+      <c r="I77" s="97"/>
+      <c r="J77" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="K77" s="95"/>
-      <c r="L77" s="95"/>
-      <c r="M77" s="95"/>
-      <c r="N77" s="95"/>
-      <c r="O77" s="95"/>
-      <c r="P77" s="95"/>
-      <c r="Q77" s="95"/>
-      <c r="R77" s="95"/>
-      <c r="S77" s="95"/>
-      <c r="T77" s="97"/>
+      <c r="K77" s="97"/>
+      <c r="L77" s="97"/>
+      <c r="M77" s="97"/>
+      <c r="N77" s="97"/>
+      <c r="O77" s="97"/>
+      <c r="P77" s="97"/>
+      <c r="Q77" s="97"/>
+      <c r="R77" s="97"/>
+      <c r="S77" s="97"/>
+      <c r="T77" s="99"/>
     </row>
     <row r="78" s="1" customFormat="1" ht="23.25" customHeight="1" spans="1:20">
-      <c r="B78" s="98"/>
-      <c r="M78" s="98"/>
-      <c r="R78" s="98"/>
+      <c r="B78" s="100"/>
+      <c r="M78" s="100"/>
+      <c r="R78" s="100"/>
     </row>
     <row r="79" s="1" customFormat="1" ht="23.25" customHeight="1" spans="1:20">
-      <c r="B79" s="99" t="s">
+      <c r="B79" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="C79" s="100" t="s">
+      <c r="C79" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="D79" s="100"/>
-      <c r="E79" s="100"/>
-      <c r="F79" s="100"/>
-      <c r="G79" s="101"/>
-      <c r="H79" s="102" t="s">
+      <c r="D79" s="102"/>
+      <c r="E79" s="102"/>
+      <c r="F79" s="102"/>
+      <c r="G79" s="103"/>
+      <c r="H79" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="I79" s="103"/>
-      <c r="K79" s="103"/>
-      <c r="L79" s="99"/>
-      <c r="M79" s="99" t="s">
+      <c r="I79" s="105"/>
+      <c r="K79" s="105"/>
+      <c r="L79" s="101"/>
+      <c r="M79" s="101" t="s">
         <v>39</v>
       </c>
-      <c r="N79" s="100"/>
-      <c r="O79" s="100"/>
-      <c r="P79" s="100"/>
-      <c r="Q79" s="104"/>
-      <c r="R79" s="99" t="s">
+      <c r="N79" s="102"/>
+      <c r="O79" s="102"/>
+      <c r="P79" s="102"/>
+      <c r="Q79" s="106"/>
+      <c r="R79" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="S79" s="104"/>
-      <c r="T79" s="104"/>
+      <c r="S79" s="106"/>
+      <c r="T79" s="106"/>
     </row>
     <row r="80" s="1" customFormat="1" ht="14.25" spans="1:20">
-      <c r="L80" s="105"/>
-    </row>
-    <row r="81" s="1" customFormat="1" ht="12.75"/>
+      <c r="D80" s="107"/>
+      <c r="E80" s="107"/>
+      <c r="L80" s="108"/>
+    </row>
+    <row r="81" s="1" customFormat="1" ht="12.75" spans="4:5">
+      <c r="D81" s="107"/>
+      <c r="E81" s="107"/>
+    </row>
+    <row r="82" spans="4:5">
+      <c r="D82" s="107"/>
+      <c r="E82" s="107"/>
+    </row>
+    <row r="83" spans="4:5">
+      <c r="D83" s="107"/>
+      <c r="E83" s="107"/>
+    </row>
   </sheetData>
-  <mergeCells count="84">
+  <mergeCells count="85">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="A5:B5"/>
@@ -4637,6 +4698,7 @@
     <mergeCell ref="A12:B17"/>
     <mergeCell ref="A10:B11"/>
     <mergeCell ref="A2:T3"/>
+    <mergeCell ref="D80:E83"/>
   </mergeCells>
   <pageMargins left="0.279861111111111" right="0.110416666666667" top="0.107638888888889" bottom="0.0305555555555556" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="33" orientation="portrait"/>

--- a/assets/MAU_BURN_TEST_REPORT.xlsx
+++ b/assets/MAU_BURN_TEST_REPORT.xlsx
@@ -1407,7 +1407,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1599,6 +1599,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4348,7 +4351,7 @@
       <c r="G69" s="61"/>
       <c r="H69" s="61"/>
       <c r="I69" s="61"/>
-      <c r="J69"/>
+      <c r="J69" s="64"/>
       <c r="K69" s="61"/>
       <c r="L69" s="61"/>
       <c r="M69" s="61"/>
@@ -4361,256 +4364,256 @@
       <c r="T69" s="62"/>
     </row>
     <row r="70" s="1" customFormat="1" ht="29.1" customHeight="1" spans="1:20">
-      <c r="A70" s="64" t="s">
+      <c r="A70" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="B70" s="65"/>
-      <c r="C70" s="65"/>
-      <c r="D70" s="66"/>
-      <c r="E70" s="67"/>
-      <c r="F70" s="68"/>
-      <c r="G70" s="69"/>
-      <c r="H70" s="70"/>
-      <c r="I70" s="71"/>
-      <c r="J70" s="72"/>
-      <c r="K70" s="72"/>
-      <c r="L70" s="73"/>
-      <c r="M70" s="69"/>
-      <c r="N70" s="70"/>
-      <c r="O70" s="71"/>
-      <c r="P70" s="72"/>
-      <c r="Q70" s="72"/>
-      <c r="R70" s="73"/>
-      <c r="S70" s="69"/>
-      <c r="T70" s="74"/>
+      <c r="B70" s="66"/>
+      <c r="C70" s="66"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="68"/>
+      <c r="F70" s="69"/>
+      <c r="G70" s="70"/>
+      <c r="H70" s="71"/>
+      <c r="I70" s="72"/>
+      <c r="J70" s="73"/>
+      <c r="K70" s="73"/>
+      <c r="L70" s="74"/>
+      <c r="M70" s="70"/>
+      <c r="N70" s="71"/>
+      <c r="O70" s="72"/>
+      <c r="P70" s="73"/>
+      <c r="Q70" s="73"/>
+      <c r="R70" s="74"/>
+      <c r="S70" s="70"/>
+      <c r="T70" s="75"/>
     </row>
     <row r="71" s="1" customFormat="1" ht="29.1" customHeight="1" spans="1:20">
-      <c r="A71" s="64" t="s">
+      <c r="A71" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="B71" s="65"/>
-      <c r="C71" s="65"/>
-      <c r="D71" s="66"/>
-      <c r="E71" s="67"/>
-      <c r="F71" s="68"/>
-      <c r="G71" s="75"/>
-      <c r="H71" s="76"/>
-      <c r="I71" s="71"/>
-      <c r="J71" s="72"/>
-      <c r="K71" s="72"/>
-      <c r="L71" s="73"/>
-      <c r="M71" s="75"/>
-      <c r="N71" s="76"/>
-      <c r="O71" s="71"/>
-      <c r="P71" s="72"/>
-      <c r="Q71" s="72"/>
-      <c r="R71" s="73"/>
-      <c r="S71" s="75"/>
-      <c r="T71" s="77"/>
+      <c r="B71" s="66"/>
+      <c r="C71" s="66"/>
+      <c r="D71" s="67"/>
+      <c r="E71" s="68"/>
+      <c r="F71" s="69"/>
+      <c r="G71" s="76"/>
+      <c r="H71" s="77"/>
+      <c r="I71" s="72"/>
+      <c r="J71" s="73"/>
+      <c r="K71" s="73"/>
+      <c r="L71" s="74"/>
+      <c r="M71" s="76"/>
+      <c r="N71" s="77"/>
+      <c r="O71" s="72"/>
+      <c r="P71" s="73"/>
+      <c r="Q71" s="73"/>
+      <c r="R71" s="74"/>
+      <c r="S71" s="76"/>
+      <c r="T71" s="78"/>
     </row>
     <row r="72" s="1" customFormat="1" ht="29.1" customHeight="1" spans="1:20">
-      <c r="A72" s="64" t="s">
+      <c r="A72" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="B72" s="65"/>
-      <c r="C72" s="65"/>
-      <c r="D72" s="71"/>
-      <c r="E72" s="72"/>
-      <c r="F72" s="73"/>
-      <c r="G72" s="75"/>
-      <c r="H72" s="76"/>
-      <c r="I72" s="71"/>
-      <c r="J72" s="72"/>
-      <c r="K72" s="72"/>
-      <c r="L72" s="73"/>
-      <c r="M72" s="75"/>
-      <c r="N72" s="76"/>
-      <c r="O72" s="71"/>
-      <c r="P72" s="72"/>
-      <c r="Q72" s="72"/>
-      <c r="R72" s="73"/>
-      <c r="S72" s="75"/>
-      <c r="T72" s="77"/>
+      <c r="B72" s="66"/>
+      <c r="C72" s="66"/>
+      <c r="D72" s="72"/>
+      <c r="E72" s="73"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="76"/>
+      <c r="H72" s="77"/>
+      <c r="I72" s="72"/>
+      <c r="J72" s="73"/>
+      <c r="K72" s="73"/>
+      <c r="L72" s="74"/>
+      <c r="M72" s="76"/>
+      <c r="N72" s="77"/>
+      <c r="O72" s="72"/>
+      <c r="P72" s="73"/>
+      <c r="Q72" s="73"/>
+      <c r="R72" s="74"/>
+      <c r="S72" s="76"/>
+      <c r="T72" s="78"/>
     </row>
     <row r="73" s="1" customFormat="1" ht="29.1" customHeight="1" spans="1:20">
-      <c r="A73" s="64" t="s">
+      <c r="A73" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="B73" s="78"/>
-      <c r="C73" s="78"/>
-      <c r="D73" s="71"/>
-      <c r="E73" s="72"/>
-      <c r="F73" s="73"/>
-      <c r="G73" s="79"/>
-      <c r="H73" s="80"/>
-      <c r="I73" s="71"/>
-      <c r="J73" s="72"/>
-      <c r="K73" s="72"/>
-      <c r="L73" s="73"/>
-      <c r="M73" s="79"/>
-      <c r="N73" s="80"/>
-      <c r="O73" s="71"/>
-      <c r="P73" s="72"/>
-      <c r="Q73" s="72"/>
-      <c r="R73" s="73"/>
-      <c r="S73" s="79"/>
-      <c r="T73" s="81"/>
+      <c r="B73" s="79"/>
+      <c r="C73" s="79"/>
+      <c r="D73" s="72"/>
+      <c r="E73" s="73"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="80"/>
+      <c r="H73" s="81"/>
+      <c r="I73" s="72"/>
+      <c r="J73" s="73"/>
+      <c r="K73" s="73"/>
+      <c r="L73" s="74"/>
+      <c r="M73" s="80"/>
+      <c r="N73" s="81"/>
+      <c r="O73" s="72"/>
+      <c r="P73" s="73"/>
+      <c r="Q73" s="73"/>
+      <c r="R73" s="74"/>
+      <c r="S73" s="80"/>
+      <c r="T73" s="82"/>
     </row>
     <row r="74" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:20">
-      <c r="A74" s="82" t="s">
+      <c r="A74" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="B74" s="83"/>
-      <c r="C74" s="83"/>
-      <c r="D74" s="83"/>
-      <c r="E74" s="83"/>
-      <c r="F74" s="83"/>
-      <c r="G74" s="83"/>
-      <c r="H74" s="83"/>
-      <c r="I74" s="83"/>
-      <c r="J74" s="83"/>
-      <c r="K74" s="83"/>
-      <c r="L74" s="83"/>
-      <c r="M74" s="83"/>
-      <c r="N74" s="83"/>
-      <c r="O74" s="83"/>
-      <c r="P74" s="83"/>
-      <c r="Q74" s="83"/>
-      <c r="R74" s="83"/>
-      <c r="S74" s="83"/>
-      <c r="T74" s="84"/>
+      <c r="B74" s="84"/>
+      <c r="C74" s="84"/>
+      <c r="D74" s="84"/>
+      <c r="E74" s="84"/>
+      <c r="F74" s="84"/>
+      <c r="G74" s="84"/>
+      <c r="H74" s="84"/>
+      <c r="I74" s="84"/>
+      <c r="J74" s="84"/>
+      <c r="K74" s="84"/>
+      <c r="L74" s="84"/>
+      <c r="M74" s="84"/>
+      <c r="N74" s="84"/>
+      <c r="O74" s="84"/>
+      <c r="P74" s="84"/>
+      <c r="Q74" s="84"/>
+      <c r="R74" s="84"/>
+      <c r="S74" s="84"/>
+      <c r="T74" s="85"/>
     </row>
     <row r="75" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:20">
-      <c r="A75" s="82" t="s">
+      <c r="A75" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="B75" s="83"/>
-      <c r="C75" s="83"/>
-      <c r="D75" s="83"/>
-      <c r="E75" s="83"/>
-      <c r="F75" s="83"/>
-      <c r="G75" s="83"/>
-      <c r="H75" s="83"/>
-      <c r="I75" s="83" t="s">
+      <c r="B75" s="84"/>
+      <c r="C75" s="84"/>
+      <c r="D75" s="84"/>
+      <c r="E75" s="84"/>
+      <c r="F75" s="84"/>
+      <c r="G75" s="84"/>
+      <c r="H75" s="84"/>
+      <c r="I75" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="J75" s="85"/>
-      <c r="K75" s="85"/>
-      <c r="L75" s="85"/>
-      <c r="M75" s="85"/>
-      <c r="N75" s="85"/>
-      <c r="O75" s="85"/>
-      <c r="P75" s="83" t="s">
+      <c r="J75" s="86"/>
+      <c r="K75" s="86"/>
+      <c r="L75" s="86"/>
+      <c r="M75" s="86"/>
+      <c r="N75" s="86"/>
+      <c r="O75" s="86"/>
+      <c r="P75" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="Q75" s="85"/>
-      <c r="R75" s="85"/>
-      <c r="S75" s="85"/>
-      <c r="T75" s="86"/>
+      <c r="Q75" s="86"/>
+      <c r="R75" s="86"/>
+      <c r="S75" s="86"/>
+      <c r="T75" s="87"/>
     </row>
     <row r="76" s="1" customFormat="1" ht="114.95" customHeight="1" spans="1:20">
-      <c r="A76" s="87"/>
-      <c r="B76" s="88"/>
-      <c r="C76" s="88"/>
-      <c r="D76" s="88"/>
-      <c r="E76" s="88"/>
-      <c r="F76" s="88"/>
-      <c r="G76" s="89"/>
-      <c r="H76" s="90"/>
-      <c r="I76" s="91"/>
-      <c r="J76" s="91"/>
-      <c r="K76" s="91"/>
-      <c r="L76" s="91"/>
-      <c r="M76" s="91"/>
-      <c r="N76" s="91"/>
-      <c r="O76" s="92"/>
-      <c r="P76" s="93"/>
-      <c r="Q76" s="93"/>
-      <c r="R76" s="93"/>
-      <c r="S76" s="93"/>
-      <c r="T76" s="94"/>
+      <c r="A76" s="88"/>
+      <c r="B76" s="89"/>
+      <c r="C76" s="89"/>
+      <c r="D76" s="89"/>
+      <c r="E76" s="89"/>
+      <c r="F76" s="89"/>
+      <c r="G76" s="90"/>
+      <c r="H76" s="91"/>
+      <c r="I76" s="92"/>
+      <c r="J76" s="92"/>
+      <c r="K76" s="92"/>
+      <c r="L76" s="92"/>
+      <c r="M76" s="92"/>
+      <c r="N76" s="92"/>
+      <c r="O76" s="93"/>
+      <c r="P76" s="94"/>
+      <c r="Q76" s="94"/>
+      <c r="R76" s="94"/>
+      <c r="S76" s="94"/>
+      <c r="T76" s="95"/>
     </row>
     <row r="77" ht="30.95" customHeight="1" spans="1:20">
-      <c r="A77" s="95"/>
-      <c r="B77" s="96"/>
-      <c r="C77" s="96"/>
-      <c r="D77" s="97" t="s">
+      <c r="A77" s="96"/>
+      <c r="B77" s="97"/>
+      <c r="C77" s="97"/>
+      <c r="D77" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="E77" s="97"/>
-      <c r="F77" s="98" t="s">
+      <c r="E77" s="98"/>
+      <c r="F77" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="G77" s="97"/>
-      <c r="H77" s="97" t="s">
+      <c r="G77" s="98"/>
+      <c r="H77" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="I77" s="97"/>
-      <c r="J77" s="98" t="s">
+      <c r="I77" s="98"/>
+      <c r="J77" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="K77" s="97"/>
-      <c r="L77" s="97"/>
-      <c r="M77" s="97"/>
-      <c r="N77" s="97"/>
-      <c r="O77" s="97"/>
-      <c r="P77" s="97"/>
-      <c r="Q77" s="97"/>
-      <c r="R77" s="97"/>
-      <c r="S77" s="97"/>
-      <c r="T77" s="99"/>
+      <c r="K77" s="98"/>
+      <c r="L77" s="98"/>
+      <c r="M77" s="98"/>
+      <c r="N77" s="98"/>
+      <c r="O77" s="98"/>
+      <c r="P77" s="98"/>
+      <c r="Q77" s="98"/>
+      <c r="R77" s="98"/>
+      <c r="S77" s="98"/>
+      <c r="T77" s="100"/>
     </row>
     <row r="78" s="1" customFormat="1" ht="23.25" customHeight="1" spans="1:20">
-      <c r="B78" s="100"/>
-      <c r="M78" s="100"/>
-      <c r="R78" s="100"/>
+      <c r="B78" s="101"/>
+      <c r="M78" s="101"/>
+      <c r="R78" s="101"/>
     </row>
     <row r="79" s="1" customFormat="1" ht="23.25" customHeight="1" spans="1:20">
-      <c r="B79" s="101" t="s">
+      <c r="B79" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="C79" s="102" t="s">
+      <c r="C79" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="D79" s="102"/>
-      <c r="E79" s="102"/>
-      <c r="F79" s="102"/>
-      <c r="G79" s="103"/>
-      <c r="H79" s="104" t="s">
+      <c r="D79" s="103"/>
+      <c r="E79" s="103"/>
+      <c r="F79" s="103"/>
+      <c r="G79" s="104"/>
+      <c r="H79" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="I79" s="105"/>
-      <c r="K79" s="105"/>
-      <c r="L79" s="101"/>
-      <c r="M79" s="101" t="s">
+      <c r="I79" s="106"/>
+      <c r="K79" s="106"/>
+      <c r="L79" s="102"/>
+      <c r="M79" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="N79" s="102"/>
-      <c r="O79" s="102"/>
-      <c r="P79" s="102"/>
-      <c r="Q79" s="106"/>
-      <c r="R79" s="101" t="s">
+      <c r="N79" s="103"/>
+      <c r="O79" s="103"/>
+      <c r="P79" s="103"/>
+      <c r="Q79" s="107"/>
+      <c r="R79" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="S79" s="106"/>
-      <c r="T79" s="106"/>
+      <c r="S79" s="107"/>
+      <c r="T79" s="107"/>
     </row>
     <row r="80" s="1" customFormat="1" ht="14.25" spans="1:20">
-      <c r="D80" s="107"/>
-      <c r="E80" s="107"/>
-      <c r="L80" s="108"/>
+      <c r="D80" s="108"/>
+      <c r="E80" s="108"/>
+      <c r="L80" s="109"/>
     </row>
     <row r="81" s="1" customFormat="1" ht="12.75" spans="4:5">
-      <c r="D81" s="107"/>
-      <c r="E81" s="107"/>
+      <c r="D81" s="108"/>
+      <c r="E81" s="108"/>
     </row>
     <row r="82" spans="4:5">
-      <c r="D82" s="107"/>
-      <c r="E82" s="107"/>
+      <c r="D82" s="108"/>
+      <c r="E82" s="108"/>
     </row>
     <row r="83" spans="4:5">
-      <c r="D83" s="107"/>
-      <c r="E83" s="107"/>
+      <c r="D83" s="108"/>
+      <c r="E83" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="85">
